--- a/12_Equity_Finance/_template_BASE.xlsx
+++ b/12_Equity_Finance/_template_BASE.xlsx
@@ -15,8 +15,11 @@
     <sheet name="CF" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="DCF" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Comps" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Sensitivity" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="RefreshLog" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Valuation Cross-Check" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Sensitivity" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="RefreshLog" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Sources" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Checks" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="172">
   <si>
     <t xml:space="preserve">[TICKER] — Company Name</t>
   </si>
@@ -363,6 +366,60 @@
     <t xml:space="preserve">Median</t>
   </si>
   <si>
+    <t xml:space="preserve">DCF vs. Comps: Valuation Triangulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No banker trusts a DCF in isolation -- the terminal value assumption alone can swing it wildly. This applies the Comps tab's own median multiples to the company's own financials to get a SECOND, independent valuation estimate, then compares it to the DCF. A large gap isn't necessarily wrong, but it means the DCF's growth/WACC/terminal-growth assumptions are pricing in something the market's current multiples for comparable companies are not -- and that's worth a second look, not an automatic override of either number.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From the DCF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCF-implied value/share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net debt (same figure as the DCF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Comps (median multiples x this company's own financials)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company FY1E revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company FY1E EBITDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comps median EV/Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comps median EV/EBITDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comps-implied EV (EV/Revenue method)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comps-implied EV (EV/EBITDA method)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comps-implied EV (average of both methods)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comps-implied equity value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comps-implied value/share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triangulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCF vs. Comps: premium/(discount)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large positive = DCF is pricing in more than the market currently pays for comparable companies; large negative = the opposite. Investigate the gap, don't just average it away.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sensitivity — Implied Value/Share</t>
   </si>
   <si>
@@ -388,18 +445,121 @@
   </si>
   <si>
     <t xml:space="preserve">Next check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What each material assumption or convention in this model comes from.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption / convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCF vs. Comps valuation triangulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard sell-side/buy-side practice: no single valuation method is trusted in isolation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A gap between methods is a prompt to investigate, not a signal either number is wrong -- comps and DCF answer related but distinct questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlevered FCF = EBIT x (1-tax) + D&amp;A - Capex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard DCF unlevered free cash flow build</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uses the IS's EBIT/D&amp;A rather than CF's levered FCF, which nets out interest -- a DCF wants the unlevered figure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comps-implied EV blended as a simple average of the EV/Revenue and EV/EBITDA methods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modeling choice for this template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modeling choice, not a universal convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A weighted blend (e.g. favoring EV/EBITDA for a mature business) may be more appropriate depending on the company -- simple average is the template default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest expense held flat at the last actual (no debt schedule)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simplification documented directly on the IS tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modeling choice, stated on the sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avoids a circular reference to a Balance Sheet debt schedule this simplified template doesn't build -- a real deal model needs an actual debt schedule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live reconciliation identities -- independent of the model's own formulas, must tie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passes when</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance sheet balances (Assets = Liabilities + Equity) across every projected year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (exact) once the Balance Sheet is populated -- BS!row19 is this template's own balance-check row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comps-implied value/share is positive whenever both multiples and financials are populated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCF terminal value uses the SAME terminal growth rate as its own discount-rate spread (WACC &gt; terminal growth, not a divide-by-negative)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE -- the Gordon Growth terminal-value formula is undefined/nonsensical when WACC &lt;= terminal growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CF's Net income and D&amp;A tie exactly to the IS (cross-sheet link, not a re-entered duplicate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (exact) -- confirms the green cross-sheet links actually pull the IS figures, not stale hardcodes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0\x"/>
+    <numFmt numFmtId="169" formatCode="General"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -559,7 +719,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -676,11 +836,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1068,6 +1252,325 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A2:F14"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:E9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="17" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>158</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:D9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="17" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="36" t="n">
+        <f aca="false">SUMPRODUCT(ABS(BS!C19:G19))</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="36" t="b">
+        <f aca="false">IF(AND(ISNUMBER('Valuation Cross-Check'!C19),'Valuation Cross-Check'!C11&gt;0,'Valuation Cross-Check'!C13&gt;0),'Valuation Cross-Check'!C19&gt;0,TRUE())</f>
+        <v>1</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="36" t="b">
+        <f aca="false">IF(DCF!I5&gt;DCF!I6,TRUE(),FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="C9" s="36" t="n">
+        <f aca="false">SUMPRODUCT(ABS(CF!E5:G5-IS!F18:H18))+SUMPRODUCT(ABS(CF!E6:G6-IS!F13:H13))</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>171</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -2733,12 +3236,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:G9"/>
+  <dimension ref="B2:D22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2746,124 +3250,144 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="28" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="C4" s="29" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="D4" s="29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E4" s="29" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F4" s="29" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G4" s="29" t="n">
-        <v>0.035</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="29" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C5" s="17" t="s">
+      <c r="B5" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="D5" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>113</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="29" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>113</v>
+      <c r="B6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <f aca="false">DCF!I14</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>113</v>
+      <c r="B7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <f aca="false">DCF!I11</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="29" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="29" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>113</v>
+      <c r="B8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <f aca="false">DCF!I13</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <f aca="false">IS!F5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <f aca="false">IS!F11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="29" t="n">
+        <f aca="false">Comps!F13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" s="29" t="n">
+        <f aca="false">Comps!G13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <f aca="false">C11*C13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <f aca="false">C12*C14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <f aca="false">AVERAGE(C15,C16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <f aca="false">C17-C7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <f aca="false">IFERROR(C18/C8,"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="28" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="31" t="str">
+        <f aca="false">IFERROR(C6/C19-1,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2882,108 +3406,138 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:F14"/>
+  <dimension ref="B2:G9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>119</v>
+      <c r="B4" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="32" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D4" s="32" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E4" s="32" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F4" s="32" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G4" s="32" t="n">
+        <v>0.035</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
+      <c r="B5" s="32" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
+      <c r="B6" s="32" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
+      <c r="B7" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
+      <c r="B8" s="32" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
+      <c r="B9" s="32" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>131</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
